--- a/src/main/resources/public/template_export/BCKCHT_173.xlsx
+++ b/src/main/resources/public/template_export/BCKCHT_173.xlsx
@@ -154,9 +154,6 @@
     <t>${item.tamHieuLucRadar.asText()}</t>
   </si>
   <si>
-    <t>${thiz.getCateOtherText('AUTH_ORG',item.fkDonViQl.asText())} - ${thiz.getCateOtherText('AUTH_ORG',item.fkDonViKt.asText())}</t>
-  </si>
-  <si>
     <t>Năm: ${bcMaText}</t>
   </si>
   <si>
@@ -169,10 +166,13 @@
     <t>${item.chieuCaoThapRadar.asText()}</t>
   </si>
   <si>
-    <t>${thiz.getCateOtherText('DM_DON_VI_HANH_CHINH',item.diaDiem.asText())}</t>
-  </si>
-  <si>
-    <t>${thiz.getCateOtherText('DM_DON_VI_HANH_CHINH',item.viTriDiaDanh.asText())}</t>
+    <t>${this.getCateOtherText('AUTH_ORG',item.fkDonViQl.asText())} - ${this.getCateOtherText('AUTH_ORG',item.fkDonViKt.asText())}</t>
+  </si>
+  <si>
+    <t>${this.getCateOtherText('DM_DON_VI_HANH_CHINH',item.diaDiem.asText())}</t>
+  </si>
+  <si>
+    <t>${this.getCateOtherText('DM_DON_VI_HANH_CHINH',item.viTriDiaDanh.asText())}</t>
   </si>
 </sst>
 </file>
@@ -311,6 +311,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -319,24 +337,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,101 +627,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="G1" s="16" t="s">
+      <c r="C1" s="14"/>
+      <c r="G1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="G2" s="15" t="s">
+      <c r="C2" s="13"/>
+      <c r="G2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="G3" s="16" t="s">
+      <c r="C3" s="13"/>
+      <c r="G3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
+      <c r="A7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
+      <c r="A8" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" spans="1:9" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="3" t="s">
         <v>16</v>
       </c>
@@ -772,7 +772,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>23</v>
@@ -780,66 +780,66 @@
       <c r="E13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="12" t="s">
         <v>28</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>29</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="F15" s="14" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="F15" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="F16" s="13" t="s">
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="F16" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
@@ -849,6 +849,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D18"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I18"/>
+    <mergeCell ref="G4:I4"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B3:C3"/>
@@ -863,11 +868,6 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D18"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I18"/>
-    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="58" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
